--- a/data/trans_camb/P1413-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1413-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -1,58</t>
+          <t>-11,17; -1,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,82</t>
+          <t>-7,78; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,62</t>
+          <t>-6,7; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 14,47</t>
+          <t>1,36; 14,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 12,45</t>
+          <t>-0,63; 12,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 2,63</t>
+          <t>-7,92; 2,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,25</t>
+          <t>-4,03; 4,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,35</t>
+          <t>-2,46; 5,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,42</t>
+          <t>-5,93; 1,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,39%</t>
+          <t>-13,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,75%</t>
+          <t>-17,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,14%</t>
+          <t>-15,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,21; -10,75</t>
+          <t>-74,09; -13,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 32,12</t>
+          <t>-50,94; 41,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 40,55</t>
+          <t>-45,55; 45,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 126,92</t>
+          <t>6,55; 133,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 115,41</t>
+          <t>-4,5; 114,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 26,0</t>
+          <t>-43,5; 20,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 47,12</t>
+          <t>-26,42; 45,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 46,52</t>
+          <t>-16,98; 53,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 14,47</t>
+          <t>-37,1; 12,68</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-6,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,05</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-4,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -11,67</t>
+          <t>-20,38; -11,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,49; -13,09</t>
+          <t>-21,19; -13,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -1,04</t>
+          <t>-11,87; -1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,86; -15,67</t>
+          <t>-26,22; -15,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -21,72</t>
+          <t>-31,13; -21,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 1,86</t>
+          <t>-9,0; 1,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -15,04</t>
+          <t>-21,72; -14,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,05; -18,61</t>
+          <t>-24,78; -18,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -1,24</t>
+          <t>-8,84; -1,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-31,71%</t>
+          <t>-30,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,16%</t>
+          <t>-10,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,35%</t>
+          <t>-18,13%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,79; -61,43</t>
+          <t>-83,18; -60,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,55; -66,32</t>
+          <t>-86,14; -68,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,64; -5,3</t>
+          <t>-50,43; -8,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -51,19</t>
+          <t>-71,73; -51,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,91; -70,15</t>
+          <t>-85,55; -70,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 6,05</t>
+          <t>-24,72; 5,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,28; -58,8</t>
+          <t>-74,61; -59,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,22; -72,51</t>
+          <t>-84,15; -72,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -5,14</t>
+          <t>-29,99; -4,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,21</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,73</t>
+          <t>12,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,93</t>
+          <t>-5,39; 3,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 3,13</t>
+          <t>-5,09; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 15,99</t>
+          <t>6,05; 15,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,34</t>
+          <t>-4,66; 6,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,32</t>
+          <t>-4,67; 6,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 19,85</t>
+          <t>8,71; 19,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,38</t>
+          <t>-3,64; 3,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,32</t>
+          <t>-3,35; 3,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,64</t>
+          <t>9,25; 16,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130,22%</t>
+          <t>131,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>100,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>111,66%</t>
+          <t>112,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 49,74</t>
+          <t>-49,66; 49,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 55,1</t>
+          <t>-47,41; 61,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,65; 257,84</t>
+          <t>52,6; 238,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 55,94</t>
+          <t>-28,34; 53,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 55,85</t>
+          <t>-28,79; 54,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,0; 174,27</t>
+          <t>49,36; 171,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 36,49</t>
+          <t>-27,07; 37,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 35,4</t>
+          <t>-26,16; 36,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67,6; 172,83</t>
+          <t>67,95; 170,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-5,33</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>16,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>5,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,1; -4,35</t>
+          <t>-14,63; -4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,47; -6,61</t>
+          <t>-16,49; -5,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 2,72</t>
+          <t>-10,76; 0,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 12,73</t>
+          <t>2,51; 12,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 10,11</t>
+          <t>-0,52; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 18,03</t>
+          <t>10,79; 21,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,09</t>
+          <t>-4,61; 3,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,94</t>
+          <t>-6,43; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 9,42</t>
+          <t>2,04; 9,88</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,32%</t>
+          <t>-27,84%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>120,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,48; -24,57</t>
+          <t>-65,79; -23,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,37; -39,03</t>
+          <t>-74,03; -34,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 17,12</t>
+          <t>-49,21; 3,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 115,57</t>
+          <t>15,38; 124,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 92,79</t>
+          <t>-4,07; 90,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 154,26</t>
+          <t>65,81; 190,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 23,01</t>
+          <t>-24,64; 21,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 5,89</t>
+          <t>-35,85; 4,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 62,62</t>
+          <t>10,77; 69,77</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 15,46</t>
+          <t>3,53; 15,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 8,78</t>
+          <t>-1,81; 8,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,07</t>
+          <t>4,34; 14,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,79; 26,2</t>
+          <t>10,13; 26,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,57</t>
+          <t>-6,61; 6,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 14,48</t>
+          <t>2,16; 14,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,99; 18,52</t>
+          <t>8,43; 19,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,09</t>
+          <t>-2,58; 6,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,35</t>
+          <t>4,88; 13,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173,08%</t>
+          <t>165,94%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>34,94; 460,48</t>
+          <t>33,4; 430,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 254,86</t>
+          <t>-24,05; 219,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56,7; 411,56</t>
+          <t>48,9; 437,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60,1; 251,94</t>
+          <t>55,35; 257,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 76,61</t>
+          <t>-37,76; 68,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,24; 145,91</t>
+          <t>10,85; 147,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,74; 229,48</t>
+          <t>67,43; 239,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 83,22</t>
+          <t>-22,96; 77,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>42,05; 175,19</t>
+          <t>37,88; 174,91</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,94</t>
+          <t>12,37</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,18</t>
+          <t>21,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,92</t>
+          <t>16,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,44</t>
+          <t>-5,47; 6,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 1,27</t>
+          <t>-9,29; 1,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,02; 19,02</t>
+          <t>6,2; 17,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 8,88</t>
+          <t>-3,56; 9,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 2,43</t>
+          <t>-9,22; 1,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,27; 27,52</t>
+          <t>14,38; 27,1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,06</t>
+          <t>-2,59; 5,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,24</t>
+          <t>-7,62; 0,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,62; 21,16</t>
+          <t>12,18; 20,89</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>139,83%</t>
+          <t>139,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>119,24%</t>
+          <t>117,16%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 64,62</t>
+          <t>-33,49; 65,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 14,0</t>
+          <t>-59,13; 19,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41,46; 195,95</t>
+          <t>35,73; 180,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 76,15</t>
+          <t>-21,03; 74,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,43; 19,79</t>
+          <t>-50,9; 17,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>80,14; 235,42</t>
+          <t>76,25; 230,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 50,17</t>
+          <t>-16,0; 45,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 2,23</t>
+          <t>-46,93; 6,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>72,5; 175,14</t>
+          <t>73,29; 176,25</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,97</t>
+          <t>29,63</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29,47</t>
+          <t>20,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -0,51</t>
+          <t>-7,95; -0,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,69</t>
+          <t>-9,08; -1,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,29</t>
+          <t>6,29; 15,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,69</t>
+          <t>1,95; 10,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 6,07</t>
+          <t>-1,76; 5,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,43; 66,26</t>
+          <t>25,23; 33,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,77</t>
+          <t>-1,72; 3,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,99</t>
+          <t>-4,61; 1,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19,26; 49,75</t>
+          <t>17,12; 23,88</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>305,14%</t>
+          <t>210,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>202,16%</t>
+          <t>142,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -3,62</t>
+          <t>-47,91; -5,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,23; -13,19</t>
+          <t>-54,84; -14,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38,18; 122,55</t>
+          <t>37,2; 115,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,94; 89,91</t>
+          <t>12,28; 84,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 50,3</t>
+          <t>-11,21; 47,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>179,61; 612,59</t>
+          <t>153,61; 276,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 28,77</t>
+          <t>-10,81; 29,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 7,81</t>
+          <t>-28,83; 9,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127,36; 362,67</t>
+          <t>103,34; 182,78</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -8,9</t>
+          <t>-16,1; -8,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,81; -8,47</t>
+          <t>-16,32; -8,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -1,24</t>
+          <t>-7,45; 0,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,99; -4,92</t>
+          <t>-12,77; -5,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -7,56</t>
+          <t>-15,24; -7,61</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,66</t>
+          <t>0,23; 7,97</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,89</t>
+          <t>-13,39; -8,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,28; -9,24</t>
+          <t>-14,8; -9,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 2,28</t>
+          <t>-2,17; 3,7</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-15,68%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-10,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -47,28</t>
+          <t>-70,29; -47,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,85; -46,18</t>
+          <t>-69,65; -46,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,5; -6,26</t>
+          <t>-32,63; 2,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-49,77; -22,0</t>
+          <t>-48,99; -22,29</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -34,77</t>
+          <t>-58,78; -34,73</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,22; 39,81</t>
+          <t>1,23; 37,01</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -37,94</t>
+          <t>-56,12; -38,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-60,01; -44,13</t>
+          <t>-60,72; -43,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 10,15</t>
+          <t>-9,14; 17,86</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -5,55</t>
+          <t>-8,84; -5,59</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -6,39</t>
+          <t>-9,61; -6,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,4</t>
+          <t>0,52; 4,09</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,81</t>
+          <t>-3,05; 0,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -3,41</t>
+          <t>-7,09; -3,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,69</t>
+          <t>9,58; 13,12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -2,85</t>
+          <t>-5,29; -2,89</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -5,49</t>
+          <t>-7,82; -5,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,52</t>
+          <t>5,81; 8,32</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-51,11; -36,07</t>
+          <t>-52,04; -36,15</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -41,7</t>
+          <t>-56,26; -42,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 21,62</t>
+          <t>3,08; 26,22</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 4,43</t>
+          <t>-14,68; 4,46</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-34,69; -18,42</t>
+          <t>-35,43; -18,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>50,32; 142,82</t>
+          <t>46,85; 72,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -16,5</t>
+          <t>-28,83; -16,82</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-42,67; -31,74</t>
+          <t>-42,67; -31,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>27,29; 92,86</t>
+          <t>31,45; 49,22</t>
         </is>
       </c>
     </row>
